--- a/GunfireDungeon_Godot/excel/DamageConfig@伤害类型属性.xlsx
+++ b/GunfireDungeon_Godot/excel/DamageConfig@伤害类型属性.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27360" windowHeight="14685"/>
+    <workbookView windowHeight="18800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -40,6 +40,30 @@
     <t>Color</t>
   </si>
   <si>
+    <t>ShieldReduce</t>
+  </si>
+  <si>
+    <t>ArmorReduce</t>
+  </si>
+  <si>
+    <t>HealthReduce</t>
+  </si>
+  <si>
+    <t>Critable</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>ReduceType</t>
+  </si>
+  <si>
+    <t>MinReduce</t>
+  </si>
+  <si>
+    <t>MaxReduce</t>
+  </si>
+  <si>
     <t>伤害类型id</t>
   </si>
   <si>
@@ -49,34 +73,82 @@
     <t>颜色</t>
   </si>
   <si>
+    <t>护盾减免</t>
+  </si>
+  <si>
+    <t>装甲减免</t>
+  </si>
+  <si>
+    <t>生命减免</t>
+  </si>
+  <si>
+    <t>可否暴击</t>
+  </si>
+  <si>
+    <t>额外效果</t>
+  </si>
+  <si>
+    <t>减免类型</t>
+  </si>
+  <si>
+    <t>默认减免上限</t>
+  </si>
+  <si>
+    <t>默认减免下限</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>物理</t>
-  </si>
-  <si>
-    <t>魔法</t>
-  </si>
-  <si>
-    <t>火焰</t>
-  </si>
-  <si>
-    <t>冰霜</t>
-  </si>
-  <si>
-    <t>雷电</t>
-  </si>
-  <si>
-    <t>光明</t>
-  </si>
-  <si>
-    <t>暗影</t>
-  </si>
-  <si>
-    <t>真实</t>
+    <t>float</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>object</t>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>物理伤害</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>火焰伤害</t>
+  </si>
+  <si>
+    <t>Electric</t>
+  </si>
+  <si>
+    <t>电击伤害</t>
+  </si>
+  <si>
+    <t>Chemical</t>
+  </si>
+  <si>
+    <t>化学伤害</t>
+  </si>
+  <si>
+    <t>Optical</t>
+  </si>
+  <si>
+    <t>光学伤害</t>
+  </si>
+  <si>
+    <t>DarkMatter</t>
+  </si>
+  <si>
+    <t>暗物质伤害</t>
+  </si>
+  <si>
+    <t>Explosive</t>
+  </si>
+  <si>
+    <t>爆破伤害</t>
   </si>
 </sst>
 </file>
@@ -89,7 +161,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,22 +170,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0076E3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF522ECE"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -263,7 +322,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,49 +331,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC52F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF4E00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BF7FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0083E5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF300"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5534CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFCCCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,12 +379,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -498,19 +545,28 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -631,52 +687,58 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -688,76 +750,70 @@
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -774,30 +830,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1160,16 +1200,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="2" width="24.1333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="33.475" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.0166666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.95" style="2" customWidth="1"/>
+    <col min="1" max="1" width="24.1346153846154" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.2403846153846" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.9038461538462" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.0192307692308" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.9519230769231" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.2403846153846" customWidth="1"/>
+    <col min="7" max="7" width="19.7788461538462" customWidth="1"/>
+    <col min="8" max="8" width="16.5865384615385" customWidth="1"/>
+    <col min="9" max="9" width="19.6538461538462" customWidth="1"/>
+    <col min="10" max="10" width="16.3076923076923" customWidth="1"/>
+    <col min="11" max="11" width="18.8173076923077" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31" customHeight="1" spans="1:3">
+    <row r="1" ht="31" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1179,104 +1226,303 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" ht="59" customHeight="1" spans="1:5">
+    <row r="2" ht="59" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:3">
+    <row r="3" ht="27" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" ht="17" customHeight="1" spans="1:3">
+    <row r="4" ht="17" customHeight="1" spans="1:11">
       <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C4" s="4"/>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0.8</v>
+      </c>
+      <c r="K4">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
+    <row r="5" ht="17" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5"/>
+      <c r="E5" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.8</v>
+      </c>
+      <c r="K5">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="6"/>
+    <row r="6" ht="17" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.8</v>
+      </c>
+      <c r="K6">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="7"/>
+    <row r="7" ht="17" spans="1:11">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.8</v>
+      </c>
+      <c r="K7">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8"/>
+    <row r="8" ht="17" spans="1:11">
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0.8</v>
+      </c>
+      <c r="K8">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="9"/>
+    <row r="9" ht="17" spans="1:11">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0.8</v>
+      </c>
+      <c r="K9">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="10"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="11"/>
+    <row r="10" ht="17" spans="1:11">
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0.8</v>
+      </c>
+      <c r="K10">
+        <v>-1</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D4:F10">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1287,7 +1533,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1299,7 +1545,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/GunfireDungeon_Godot/excel/DamageConfig@伤害类型属性.xlsx
+++ b/GunfireDungeon_Godot/excel/DamageConfig@伤害类型属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18800"/>
+    <workbookView windowWidth="30500" windowHeight="17840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -88,7 +88,14 @@
     <t>额外效果</t>
   </si>
   <si>
-    <t>减免类型</t>
+    <t>减免类型
+Physical（物理减免）：0
+Fire（火焰减免）：1
+Electric（电击减免）：2
+Chemical（化学减免）：3
+Optical（光学减免）：4
+DarkMatter（暗物质减免）：5
+Explosive（爆破减免）：6</t>
   </si>
   <si>
     <t>默认减免上限</t>
@@ -107,6 +114,9 @@
   </si>
   <si>
     <t>object</t>
+  </si>
+  <si>
+    <t>ReduceEnum</t>
   </si>
   <si>
     <t>Physical</t>
@@ -817,7 +827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -838,6 +848,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1211,7 +1224,7 @@
     <col min="6" max="6" width="24.2403846153846" customWidth="1"/>
     <col min="7" max="7" width="19.7788461538462" customWidth="1"/>
     <col min="8" max="8" width="16.5865384615385" customWidth="1"/>
-    <col min="9" max="9" width="19.6538461538462" customWidth="1"/>
+    <col min="9" max="9" width="36.3653846153846" customWidth="1"/>
     <col min="10" max="10" width="16.3076923076923" customWidth="1"/>
     <col min="11" max="11" width="18.8173076923077" customWidth="1"/>
   </cols>
@@ -1251,7 +1264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="59" customHeight="1" spans="1:11">
+    <row r="2" ht="144" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1276,7 +1289,7 @@
       <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J2" t="s">
@@ -1312,7 +1325,7 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
         <v>23</v>
@@ -1323,10 +1336,10 @@
     </row>
     <row r="4" ht="17" customHeight="1" spans="1:11">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5">
@@ -1341,6 +1354,9 @@
       <c r="G4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
       <c r="J4">
         <v>0.8</v>
       </c>
@@ -1350,10 +1366,10 @@
     </row>
     <row r="5" ht="17" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="5">
@@ -1368,6 +1384,9 @@
       <c r="G5" t="b">
         <v>0</v>
       </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
       <c r="J5">
         <v>0.8</v>
       </c>
@@ -1377,10 +1396,10 @@
     </row>
     <row r="6" ht="17" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="5">
@@ -1395,6 +1414,9 @@
       <c r="G6" t="b">
         <v>0</v>
       </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
       <c r="J6">
         <v>0.8</v>
       </c>
@@ -1404,10 +1426,10 @@
     </row>
     <row r="7" ht="17" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="5">
@@ -1422,6 +1444,9 @@
       <c r="G7" t="b">
         <v>0</v>
       </c>
+      <c r="I7" t="s">
+        <v>33</v>
+      </c>
       <c r="J7">
         <v>0.8</v>
       </c>
@@ -1431,10 +1456,10 @@
     </row>
     <row r="8" ht="17" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="5">
@@ -1449,6 +1474,9 @@
       <c r="G8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="s">
+        <v>35</v>
+      </c>
       <c r="J8">
         <v>0.8</v>
       </c>
@@ -1458,10 +1486,10 @@
     </row>
     <row r="9" ht="17" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="5">
@@ -1476,6 +1504,9 @@
       <c r="G9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
       <c r="J9">
         <v>0.8</v>
       </c>
@@ -1485,10 +1516,10 @@
     </row>
     <row r="10" ht="17" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="5">
@@ -1502,6 +1533,9 @@
       </c>
       <c r="G10" t="b">
         <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>39</v>
       </c>
       <c r="J10">
         <v>0.8</v>

--- a/GunfireDungeon_Godot/excel/DamageConfig@伤害类型属性.xlsx
+++ b/GunfireDungeon_Godot/excel/DamageConfig@伤害类型属性.xlsx
@@ -40,13 +40,13 @@
     <t>Color</t>
   </si>
   <si>
-    <t>ShieldReduce</t>
-  </si>
-  <si>
-    <t>ArmorReduce</t>
-  </si>
-  <si>
-    <t>HealthReduce</t>
+    <t>ShieldMultiplier</t>
+  </si>
+  <si>
+    <t>ArmorMultiplier</t>
+  </si>
+  <si>
+    <t>HealthMultiplier</t>
   </si>
   <si>
     <t>Critable</t>
@@ -73,13 +73,13 @@
     <t>颜色</t>
   </si>
   <si>
-    <t>护盾减免</t>
-  </si>
-  <si>
-    <t>装甲减免</t>
-  </si>
-  <si>
-    <t>生命减免</t>
+    <t>护盾伤害倍率</t>
+  </si>
+  <si>
+    <t>装甲伤害倍率</t>
+  </si>
+  <si>
+    <t>生命伤害倍率</t>
   </si>
   <si>
     <t>可否暴击</t>
@@ -98,10 +98,10 @@
 Explosive（爆破减免）：6</t>
   </si>
   <si>
-    <t>默认减免上限</t>
-  </si>
-  <si>
-    <t>默认减免下限</t>
+    <t>默认减免上限（倍率）</t>
+  </si>
+  <si>
+    <t>默认减免下限（倍率）</t>
   </si>
   <si>
     <t>string</t>
@@ -827,7 +827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -835,21 +835,34 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1219,14 +1232,14 @@
     <col min="1" max="1" width="24.1346153846154" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.2403846153846" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.9038461538462" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.0192307692308" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.9519230769231" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.2403846153846" customWidth="1"/>
-    <col min="7" max="7" width="19.7788461538462" customWidth="1"/>
-    <col min="8" max="8" width="16.5865384615385" customWidth="1"/>
-    <col min="9" max="9" width="36.3653846153846" customWidth="1"/>
-    <col min="10" max="10" width="16.3076923076923" customWidth="1"/>
-    <col min="11" max="11" width="18.8173076923077" customWidth="1"/>
+    <col min="4" max="4" width="25.0192307692308" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.9519230769231" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.2403846153846" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.7788461538462" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.5865384615385" style="2" customWidth="1"/>
+    <col min="9" max="9" width="36.3653846153846" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.3076923076923" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.8173076923077" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="31" customHeight="1" spans="1:11">
@@ -1239,28 +1252,28 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1274,28 +1287,28 @@
       <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1309,28 +1322,28 @@
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1351,16 +1364,16 @@
       <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" t="b">
+      <c r="G4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0.8</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1381,16 +1394,16 @@
       <c r="F5" s="5">
         <v>1.5</v>
       </c>
-      <c r="G5" t="b">
+      <c r="G5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0.8</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1411,16 +1424,16 @@
       <c r="F6" s="5">
         <v>0.5</v>
       </c>
-      <c r="G6" t="b">
+      <c r="G6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0.8</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1441,16 +1454,16 @@
       <c r="F7" s="5">
         <v>1</v>
       </c>
-      <c r="G7" t="b">
+      <c r="G7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0.8</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1471,16 +1484,16 @@
       <c r="F8" s="5">
         <v>0.5</v>
       </c>
-      <c r="G8" t="b">
+      <c r="G8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0.8</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1501,16 +1514,16 @@
       <c r="F9" s="5">
         <v>1</v>
       </c>
-      <c r="G9" t="b">
+      <c r="G9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>0.8</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1531,16 +1544,16 @@
       <c r="F10" s="5">
         <v>1.5</v>
       </c>
-      <c r="G10" t="b">
+      <c r="G10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>0.8</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>-1</v>
       </c>
     </row>

--- a/GunfireDungeon_Godot/excel/DamageConfig@伤害类型属性.xlsx
+++ b/GunfireDungeon_Godot/excel/DamageConfig@伤害类型属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30500" windowHeight="17840"/>
+    <workbookView windowHeight="19180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>MaxReduce</t>
   </si>
   <si>
-    <t>伤害类型id</t>
+    <t>伤害类型id,和DamageType枚举名称对应</t>
   </si>
   <si>
     <t>名称</t>
